--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -900,7 +900,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -917,7 +917,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -968,7 +968,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/courses - interview practice test.xlsx
+++ b/courses - interview practice test.xlsx
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>
